--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -6409,10 +6409,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119834211</v>
+        <v>119833174</v>
       </c>
       <c r="B53" t="n">
-        <v>91884</v>
+        <v>91848</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6421,25 +6421,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5449</v>
+        <v>2058</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620367</v>
+        <v>620433</v>
       </c>
       <c r="R53" t="n">
-        <v>6905686</v>
+        <v>6905535</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6521,10 +6521,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119833174</v>
+        <v>119834211</v>
       </c>
       <c r="B54" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6533,25 +6533,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2058</v>
+        <v>5449</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620433</v>
+        <v>620367</v>
       </c>
       <c r="R54" t="n">
-        <v>6905535</v>
+        <v>6905686</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -6412,7 +6412,7 @@
         <v>119833174</v>
       </c>
       <c r="B53" t="n">
-        <v>91848</v>
+        <v>91866</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>119834211</v>
       </c>
       <c r="B54" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -6409,10 +6409,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119833174</v>
+        <v>119834211</v>
       </c>
       <c r="B53" t="n">
-        <v>91866</v>
+        <v>91902</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6421,25 +6421,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2058</v>
+        <v>5449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620433</v>
+        <v>620367</v>
       </c>
       <c r="R53" t="n">
-        <v>6905535</v>
+        <v>6905686</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6521,10 +6521,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119834211</v>
+        <v>119833174</v>
       </c>
       <c r="B54" t="n">
-        <v>91902</v>
+        <v>91866</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6533,25 +6533,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>2058</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620367</v>
+        <v>620433</v>
       </c>
       <c r="R54" t="n">
-        <v>6905686</v>
+        <v>6905535</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6631,6 +6631,132 @@
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120499309</v>
+      </c>
+      <c r="B55" t="n">
+        <v>89232</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1594</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Svartfjällig musseron</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tricholoma atrosquamosum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sacc.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Häljum, Häljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>620405</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6905716</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>I kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6757,6 +6757,655 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120553362</v>
+      </c>
+      <c r="B56" t="n">
+        <v>94550</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>210</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Häljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>620465</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6905674</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>1 äldre kapsel, tyvärr inget foto</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120553360</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Häljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>620428</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6905631</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>112178674</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hälljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>620480</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6905672</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120553361</v>
+      </c>
+      <c r="B59" t="n">
+        <v>94550</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>210</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Häljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>620462</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6905689</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120553363</v>
+      </c>
+      <c r="B60" t="n">
+        <v>94550</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>210</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Häljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>620548</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6905540</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>2 kapslar</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120553359</v>
+      </c>
+      <c r="B61" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Häljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>620483</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6905584</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -5744,7 +5744,7 @@
         <v>115805595</v>
       </c>
       <c r="B47" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>115805548</v>
       </c>
       <c r="B48" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>115805727</v>
       </c>
       <c r="B49" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -5744,7 +5744,7 @@
         <v>115805595</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>115805548</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>115805727</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -5744,7 +5744,7 @@
         <v>115805595</v>
       </c>
       <c r="B47" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>115805548</v>
       </c>
       <c r="B48" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>115805727</v>
       </c>
       <c r="B49" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -5744,7 +5744,7 @@
         <v>115805595</v>
       </c>
       <c r="B47" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>115805548</v>
       </c>
       <c r="B48" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>115805727</v>
       </c>
       <c r="B49" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7406,6 +7406,331 @@
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127275981</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92621</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hälljum, Hälljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>620428</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6905648</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127277356</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91726</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hälljum, Hälljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>620359</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6905811</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127277326</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91615</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>658</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hälljum, Hälljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>620355</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6905810</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7411,7 +7411,7 @@
         <v>127275981</v>
       </c>
       <c r="B62" t="n">
-        <v>92621</v>
+        <v>92627</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>127277356</v>
       </c>
       <c r="B63" t="n">
-        <v>91726</v>
+        <v>91732</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>127277326</v>
       </c>
       <c r="B64" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7411,7 +7411,7 @@
         <v>127275981</v>
       </c>
       <c r="B62" t="n">
-        <v>92627</v>
+        <v>92628</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>127277356</v>
       </c>
       <c r="B63" t="n">
-        <v>91732</v>
+        <v>91733</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>127277326</v>
       </c>
       <c r="B64" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7411,7 +7411,7 @@
         <v>127275981</v>
       </c>
       <c r="B62" t="n">
-        <v>92628</v>
+        <v>92632</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>127277356</v>
       </c>
       <c r="B63" t="n">
-        <v>91733</v>
+        <v>91737</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>127277326</v>
       </c>
       <c r="B64" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7411,7 +7411,7 @@
         <v>127275981</v>
       </c>
       <c r="B62" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>127277356</v>
       </c>
       <c r="B63" t="n">
-        <v>91737</v>
+        <v>91739</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>127277326</v>
       </c>
       <c r="B64" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7411,7 +7411,7 @@
         <v>127275981</v>
       </c>
       <c r="B62" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>127277356</v>
       </c>
       <c r="B63" t="n">
-        <v>91739</v>
+        <v>91745</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>127277326</v>
       </c>
       <c r="B64" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7411,7 +7411,7 @@
         <v>127275981</v>
       </c>
       <c r="B62" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>127277356</v>
       </c>
       <c r="B63" t="n">
-        <v>91745</v>
+        <v>91748</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>127277326</v>
       </c>
       <c r="B64" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7411,7 +7411,7 @@
         <v>127275981</v>
       </c>
       <c r="B62" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>127277356</v>
       </c>
       <c r="B63" t="n">
-        <v>91748</v>
+        <v>91756</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>127277326</v>
       </c>
       <c r="B64" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7411,7 +7411,7 @@
         <v>127275981</v>
       </c>
       <c r="B62" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>127277356</v>
       </c>
       <c r="B63" t="n">
-        <v>91756</v>
+        <v>91757</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>127277326</v>
       </c>
       <c r="B64" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7731,6 +7731,440 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129628035</v>
+      </c>
+      <c r="B65" t="n">
+        <v>96169</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>210</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Häljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>620457</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6905688</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Återbesök av tidigare observation från annan observatör. Nya kapslar återfanns på lågan.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129628032</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Häljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>620435</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6905570</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129628036</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Häljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>620472</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6905575</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129628165</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hälljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>620449</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6905598</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Upprörda, varnande fåglar.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7733,49 +7733,52 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129628035</v>
+        <v>129628032</v>
       </c>
       <c r="B65" t="n">
-        <v>96169</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>210</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Häljum, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>620457</v>
+        <v>620435</v>
       </c>
       <c r="R65" t="n">
-        <v>6905688</v>
+        <v>6905570</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7802,17 +7805,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Återbesök av tidigare observation från annan observatör. Nya kapslar återfanns på lågan.</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7821,7 +7819,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7840,7 +7837,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129628032</v>
+        <v>129628036</v>
       </c>
       <c r="B66" t="n">
         <v>57727</v>
@@ -7868,27 +7865,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Häljum, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>620435</v>
+        <v>620472</v>
       </c>
       <c r="R66" t="n">
-        <v>6905570</v>
+        <v>6905575</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7944,10 +7946,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129628036</v>
+        <v>129628165</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7955,49 +7957,49 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Häljum, Mpd</t>
+          <t>Hälljum, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>620472</v>
+        <v>620449</v>
       </c>
       <c r="R67" t="n">
-        <v>6905575</v>
+        <v>6905598</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8021,12 +8023,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Upprörda, varnande fåglar.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8053,60 +8060,52 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129628165</v>
+        <v>129628035</v>
       </c>
       <c r="B68" t="n">
-        <v>57887</v>
+        <v>96169</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hälljum, Mpd</t>
+          <t>Häljum, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>620449</v>
+        <v>620457</v>
       </c>
       <c r="R68" t="n">
-        <v>6905598</v>
+        <v>6905688</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8130,17 +8129,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Upprörda, varnande fåglar.</t>
+          <t>Återbesök av tidigare observation från annan observatör. Nya kapslar återfanns på lågan.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8149,6 +8148,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7736,7 +7736,7 @@
         <v>129628032</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>129628036</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>129628165</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>129628035</v>
       </c>
       <c r="B68" t="n">
-        <v>96169</v>
+        <v>96198</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7736,7 +7736,7 @@
         <v>129628032</v>
       </c>
       <c r="B65" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>129628036</v>
       </c>
       <c r="B66" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>129628165</v>
       </c>
       <c r="B67" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>129628035</v>
       </c>
       <c r="B68" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7733,10 +7733,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129628032</v>
+        <v>129628165</v>
       </c>
       <c r="B65" t="n">
-        <v>57735</v>
+        <v>57896</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7744,44 +7744,49 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Häljum, Mpd</t>
+          <t>Hälljum, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>620435</v>
+        <v>620449</v>
       </c>
       <c r="R65" t="n">
-        <v>6905570</v>
+        <v>6905598</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7805,12 +7810,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Upprörda, varnande fåglar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7837,46 +7847,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129628036</v>
+        <v>129628035</v>
       </c>
       <c r="B66" t="n">
-        <v>57735</v>
+        <v>96211</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>210</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7884,13 +7886,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>620472</v>
+        <v>620457</v>
       </c>
       <c r="R66" t="n">
-        <v>6905575</v>
+        <v>6905688</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7914,12 +7916,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Återbesök av tidigare observation från annan observatör. Nya kapslar återfanns på lågan.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7928,6 +7935,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7946,10 +7954,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129628165</v>
+        <v>129628032</v>
       </c>
       <c r="B67" t="n">
-        <v>57895</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7957,49 +7965,44 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hälljum, Mpd</t>
+          <t>Häljum, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>620449</v>
+        <v>620435</v>
       </c>
       <c r="R67" t="n">
-        <v>6905598</v>
+        <v>6905570</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8023,17 +8026,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Upprörda, varnande fåglar.</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8060,38 +8058,46 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129628035</v>
+        <v>129628036</v>
       </c>
       <c r="B68" t="n">
-        <v>96210</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>210</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8099,13 +8105,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>620457</v>
+        <v>620472</v>
       </c>
       <c r="R68" t="n">
-        <v>6905688</v>
+        <v>6905575</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8129,17 +8135,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Återbesök av tidigare observation från annan observatör. Nya kapslar återfanns på lågan.</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8148,7 +8149,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -7850,7 +7850,7 @@
         <v>129628035</v>
       </c>
       <c r="B66" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 9864-2024 artfynd.xlsx
+++ b/artfynd/A 9864-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8165,6 +8165,297 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129800306</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91593</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Karsmon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>620390</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6905589</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129800843</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91593</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Karsmon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>620429</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6905588</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129800748</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91593</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Karsmon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>620397</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6905565</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
